--- a/public/downloads/WeiInsights2022.xlsx
+++ b/public/downloads/WeiInsights2022.xlsx
@@ -1570,16 +1570,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1857612708278573</v>
+        <v>0.183461778937577</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1764011259742255</v>
+        <v>0.1758262530016554</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1131407884531143</v>
+        <v>0.1126808900750582</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3281,16 +3281,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01729871698682928</v>
+        <v>0.01194414234623764</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.503970959986745</v>
+        <v>0.5026323163265971</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2220010768187421</v>
+        <v>0.2209301618906238</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.115155970896808</v>
+        <v>-0.04629848665527447</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2604976479427056</v>
+        <v>0.2538394265290184</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2987445437933995</v>
+        <v>0.264067542552084</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -4435,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02308562117429839</v>
+        <v>-0.1120870367870737</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4426917122875789</v>
+        <v>0.398615599910876</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1892947827164512</v>
+        <v>0.1601937714184392</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -4551,16 +4551,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2293194371953064</v>
+        <v>0.1648019538671974</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2916342116383882</v>
+        <v>0.2639838616406272</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2986369837124994</v>
+        <v>0.2857334870468776</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -5561,16 +5561,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4682043874952529</v>
+        <v>-0.3316822513743887</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4079725854716187</v>
+        <v>0.348053456195371</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4461000398769482</v>
+        <v>0.3971241972927884</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -5620,16 +5620,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4995955145229282</v>
+        <v>-0.5284099446265529</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2082408235332779</v>
+        <v>0.2041244763756172</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2082408235332779</v>
+        <v>0.2041244763756172</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -5679,16 +5679,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.161777250333169</v>
+        <v>-0.2834805887679543</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2205539318412033</v>
+        <v>0.203167740636234</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2205539318412033</v>
+        <v>0.203167740636234</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -6701,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2942011781580072</v>
+        <v>-0.1585577724547989</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3786551141296423</v>
+        <v>0.3228178098963901</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3786551141296423</v>
+        <v>0.3228178098963901</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -6760,16 +6760,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2842382790234461</v>
+        <v>-0.2460615633936527</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1200692666676475</v>
+        <v>0.1146154501491056</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1200692666676475</v>
+        <v>0.1146154501491056</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -6819,16 +6819,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1517888742606129</v>
+        <v>-0.2356957610635071</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2235592752647157</v>
+        <v>0.2036494629716432</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2235592752647157</v>
+        <v>0.2036494629716432</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7250,13 +7250,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4623022514074423</v>
+        <v>0.4571044997424909</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3116890344096299</v>
+        <v>0.3080543953041627</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3682186361482855</v>
+        <v>0.3619385801117612</v>
       </c>
       <c r="K3" s="4">
         <v>80.53526673827423</v>
@@ -7350,13 +7350,13 @@
         <v>2.631578947368421</v>
       </c>
       <c r="H5" s="4">
-        <v>0.401431601156777</v>
+        <v>0.4004921735839006</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3359230673765293</v>
+        <v>0.3347482193093229</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3503440870171342</v>
+        <v>0.3512835145900106</v>
       </c>
       <c r="K5" s="4">
         <v>82.43465807375588</v>
@@ -7450,13 +7450,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1957506751767366</v>
+        <v>0.1883183872863403</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2295695680217301</v>
+        <v>0.2221189450136544</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1928935181796309</v>
+        <v>0.2273218125842564</v>
       </c>
       <c r="K7" s="4">
         <v>89.25528105979234</v>
@@ -7500,13 +7500,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3800102479068662</v>
+        <v>0.379889222017904</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2630633810783653</v>
+        <v>0.2629281168495253</v>
       </c>
       <c r="J8" s="4">
-        <v>0.3220491185059253</v>
+        <v>0.3219280926169632</v>
       </c>
       <c r="K8" s="4">
         <v>83.7862513426424</v>
@@ -7650,13 +7650,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3982960200359048</v>
+        <v>0.3967876858470365</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2989947780664508</v>
+        <v>0.2901024204794306</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2164237102908334</v>
+        <v>0.2206463843098544</v>
       </c>
       <c r="K11" s="4">
         <v>85.8530254206941</v>
@@ -7750,13 +7750,13 @@
         <v>2.631578947368421</v>
       </c>
       <c r="H13" s="4">
-        <v>0.6820792000428836</v>
+        <v>0.6677065329639902</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3267911913489491</v>
+        <v>0.3154043555815119</v>
       </c>
       <c r="J13" s="4">
-        <v>0.4133662834369796</v>
+        <v>0.4002412180630616</v>
       </c>
       <c r="K13" s="4">
         <v>80.02953813104159</v>
@@ -7848,13 +7848,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3290125188963622</v>
+        <v>0.312436971455615</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3206739475074675</v>
+        <v>0.3057239879126939</v>
       </c>
       <c r="J15" s="4">
-        <v>0.244191326432099</v>
+        <v>0.2316873848513781</v>
       </c>
       <c r="K15" s="4">
         <v>91.13856068743287</v>
@@ -7948,13 +7948,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2813538812737735</v>
+        <v>0.2649264119172652</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3010870069244873</v>
+        <v>0.282726894114272</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2600377281452387</v>
+        <v>0.2489027556686898</v>
       </c>
       <c r="K17" s="4">
         <v>88.0227354099528</v>
@@ -9651,16 +9651,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05730496451719773</v>
+        <v>-0.1299977466265432</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3191533760459009</v>
+        <v>0.3009801805185646</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1585527658749789</v>
+        <v>0.1440142094531097</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -9767,13 +9767,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0846906859134909</v>
+        <v>0.03256168686402816</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3777187536811761</v>
+        <v>0.3702717538169671</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4050943573307298</v>
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07573940885452164</v>
+        <v>0.09627929822511305</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -10786,7 +10786,7 @@
         <v>0.236357351653453</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.246855870249296</v>
+        <v>0.2468558702492961</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -10836,16 +10836,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06460039195429447</v>
+        <v>0.09257034269069209</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1640861434053611</v>
+        <v>0.1600904361573043</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1640861434053611</v>
+        <v>0.1600904361573043</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -10895,16 +10895,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2340210599777947</v>
+        <v>0.2314449609668259</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6444717267108444</v>
+        <v>0.6433676842775721</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.500869242462827</v>
+        <v>0.5003540226606333</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -11905,16 +11905,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06460632892789622</v>
+        <v>0.187404649303005</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2062821263985443</v>
+        <v>0.1798434936485194</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.220643211455465</v>
+        <v>0.2031005942590209</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -11964,16 +11964,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.08201733641550391</v>
+        <v>0.1285728541833464</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1357911250254996</v>
+        <v>0.1256599996205198</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1357911250254996</v>
+        <v>0.1256599996205198</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
